--- a/teste_integração.xlsx
+++ b/teste_integração.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O resultado informado corresponde ao percentual de atividades concluídas em relação às atividades previstas no cronograma da iniciativa para o ano de 2024. Abaixo, estão elencadas as principais ações finalizadas no período: • Disponibilização da cartilha em braile; • Elaboração do plano anual de comunicação para as campanhas de acessibilidade e inclusão • Expansão do Projeto Amigo Down, em parceria com as APAEs para alcançar novas localidades. • Em desenvolvimento o projeto Cordão de Girassol, uma iniciativa voltada ao reconhecimento facilitados de pessoas com deficiências ocultas. Os cordões de Girassol já estão disponíveis na Gerência de Saúde no Trabalho - Gersat. • Foram realizadas visitas às comarcas de Pará de Minas, Timóteo, Águas Formosas e Baependi para avaliar a acessibilidade dos prédios, visando identificar necessidades de melhorias ou adequações. Foram identificadas as necessidades de melhorias e adequações, as quais foram enviadas às áreas responsáveis para que adotem as providências cabíveis. • Realização do Seminário Setembro Acessível: diálogos sobre inclusão no Judiciário. • Foi publicada, na aba de Transparência do Portal TJMG, a Nota Técnica sobre Inclusão Social em Contratações Públicas. • Foi realizado o estudo de viabilidade para a implantação de um balcão virtual acessível destinado ao atendimento de pessoas surdas. Posteriormente, o estudo foi consolidado e a proposta de instalação foi encaminhada à Diretoria Executiva de Suporte à Prestação Jurisdicional (DIRSUP). • Concluído o estudo para a criação de uma iniciativa voltada para jovens adultos desligados de instituições de acolhimento, elaborou-se a proposta para a apresentação e implementação do projeto. • Concluído o levantamento das necessidades de equipamentos básicos de informática e tecnologias assistivas, com a consequente elaboração de uma proposta de política sobre o tema. O documento já foi submetido à análise da área responsável.</t>
+          <t>O resultado informado corresponde ao percentual de atividades concluídas em relação às atividades previstas no cronograma da iniciativa para o ano de 2025. Abaixo, estão elencadas as principais ações finalizadas no período: • Disponibilização da cartilha em braile; • Elaboração do plano anual de comunicação para as campanhas de acessibilidade e inclusão • Expansão do Projeto Amigo Down, em parceria com as APAEs para alcançar novas localidades. • Em desenvolvimento o projeto Cordão de Girassol, uma iniciativa voltada ao reconhecimento facilitados de pessoas com deficiências ocultas. Os cordões de Girassol já estão disponíveis na Gerência de Saúde no Trabalho - Gersat. • Foram realizadas visitas às comarcas de Pará de Minas, Timóteo, Águas Formosas e Baependi para avaliar a acessibilidade dos prédios, visando identificar necessidades de melhorias ou adequações. Foram identificadas as necessidades de melhorias e adequações, as quais foram enviadas às áreas responsáveis para que adotem as providências cabíveis. • Realização do Seminário Setembro Acessível: diálogos sobre inclusão no Judiciário. • Foi publicada, na aba de Transparência do Portal TJMG, a Nota Técnica sobre Inclusão Social em Contratações Públicas. • Foi realizado o estudo de viabilidade para a implantação de um balcão virtual acessível destinado ao atendimento de pessoas surdas. Posteriormente, o estudo foi consolidado e a proposta de instalação foi encaminhada à Diretoria Executiva de Suporte à Prestação Jurisdicional (DIRSUP). • Concluído o estudo para a criação de uma iniciativa voltada para jovens adultos desligados de instituições de acolhimento, elaborou-se a proposta para a apresentação e implementação do projeto. • Concluído o levantamento das necessidades de equipamentos básicos de informática e tecnologias assistivas, com a consequente elaboração de uma proposta de política sobre o tema. O documento já foi submetido à análise da área responsável.</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>A meta  TJMG 131 previu concluir, até dezembro de 2025, as entregas relativas à validação do fluxo de implantação dos Fóruns Digitais e à alteração da Resolução 1.061/2023 (Dispõe sobre a criação, a estrutura e o funcionamento dos Fóruns e CEJUSCs Digitais, no Poder Judiciário de Minas Gerais). Até dezembro de 2025, nenhuma das duas entregas havia sido concluída, embora apresentem um estágio de desenvolvimento avançado, de forma que o valor apurado da meta até o período foi de 0%. Em relação à “alteração da Resolução 1.061/2023”,  foi elaborada uma minuta de alteração do normativo, que está em análise pela Secretaria de Governança e Gestão Estratégica – SEGOVE, para, então, ser submetida à aprovação do Órgão Especial do TJMG para sua posterior publicação. Em relação à entrega de “validação do fluxo de implantação dos Fóruns Digitais”,  uma primeira versão foi elaborada pelo CEPROC em 2024 e submetida à análise das unidades responsáveis, para proposição de adequações. O retorno das áreas se prolongou mais do que o previsto, implicando atraso na conclusão da entrega. Em junho de 2025, as tratativas foram retomadas em reunião entre o CEPROC e as unidades, ocasião em que se identificou a necessidade de novos ajustes e melhor detalhamento do fluxo. As correções solicitadas pelas áreas já foram realizadas e a nova versão foi submetida em agosto para validação da Secretaria de Governança e Gestão Estratégica – SEGOVE. Aguarda-se retorno para que a entrega seja dada como concluída.</t>
+          <t>A meta  TJMG 131 previu concluir, até dezembro de 2025, as entregas relativas à validação do fluxo de implantação dos Fóruns Digitais e à alteração da Resolução 1.061/2023 (Dispõe sobre a criação, a estrutura e o funcionamento dos Fóruns e CEJUSCs Digitais, no Poder Judiciário de Minas Gerais). Até dezembro de 2025, nenhuma das duas entregas havia sido concluída, embora apresentem um estágio de desenvolvimento avançado, de forma que o valor apurado da meta até o período foi de 0%. Em relação à “alteração da Resolução 1.061/2023”,  foi elaborada uma minuta de alteração do normativo, que está em análise pela Secretaria de Governança e Gestão Estratégica – SEGOVE, para, então, ser submetida à aprovação do Órgão Especial do TJMG para sua posterior publicação. Já no que diz respeito ao fluxo, dois processos de trabalho (Planejamento de Fóruns Digitais e Instalação de Fóruns Digitais) foram elaborados pela equipe do Centro de Gestão de Processos de Trabalho, Padronização e Qualidade - CEPROC ao longo de 2024 e submetidos às unidades envolvidas em outubro de 2024 para análise e proposição de adequação. Até maio de 2025, somente parte das áreas tinham apresentado sugestões, implicando atraso na entrega. Na intenção de retomar as discussões, no dia 26 de junho foi realizada reunião entre o CEPROC e as unidades responsáveis, ocasião em que se identificou a necessidade de novos ajustes e melhor detalhamento dos fluxos. As correções solicitadas pelas áreas foram realizadas e a nova versão foi submetida em agosto para validação da Secretaria de Governança e Gestão Estratégica – SEGOVE.</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Meta TJMG 143 : aumentar, até 18/12/2025, em pelo menos 10% (dez por cento) o número de municípios que promovem o Programa Descubra. Em relação à meta TJMG 143, considerando a adesão de 2 municípios (Ouro Preto e Timóteo) no aumento do número de municípios que promovem o Programa Descubra observa-se que a meta proposta foi alcançada. Para o ano de 2026 há manifestação de interesse dos municípios de Carandaí e Iguatama em aderir ao Programa. Lista completa de municípios já participantes do Programa Descubra:  Araxá, Belo Horizonte, Betim, Pirapora (Buritizeiro, Jequitaí), Contagem, Coronel Fabriciano, Divinópolis, Governador Valadares, Ipatinga (Santana do Paraíso), Juiz de Fora, Montes Claros, Muriaé, Ouro Preto, Passos, Patos de Minas, Pouso Alegre, Ribeirão das Neves, Sete Lagoas, Uberlândia, Uberaba (Campo Florido, Delta, Água Comprida, Veríssimo) , Timóteo e Varginha</t>
+          <t>Meta TJMG 143 : aumentar, até 18/12/2025, em pelo menos 10% (dez por cento) o número de municípios que promovem o Programa Descubra. Em relação à meta TJMG 143, considerando a adesão de 2 municípios (Ouro Preto e Timóteo) que promovem o Programa Descubra em um total de  21 municipios ( referência em março de 2025) observa-se que a meta proposta foi alcançada. Para o ano de 2026 há manifestação de interesse dos municípios de Carandaí e Iguatama em aderir ao Programa. Lista completa de municípios já participantes do Programa Descubra ( total de 23 municípios):  Araxá, Belo Horizonte, Betim, Pirapora (Buritizeiro, Jequitaí), Contagem, Coronel Fabriciano, Divinópolis, Governador Valadares, Ipatinga (Santana do Paraíso), Juiz de Fora, Montes Claros, Muriaé, Ouro Preto, Passos, Patos de Minas, Pouso Alegre, Ribeirão das Neves, Sete Lagoas, Uberlândia, Uberaba (Campo Florido, Delta, Água Comprida, Veríssimo) , Timóteo e Varginha.</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>135,419</t>
+          <t>135.419</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Até dezembro de 2025, 135.419 pessoas foram beneficiadas com ações de impacto social promovidas pela COINJ, sendo: •	198 pessoas alcançadas pelo Programa Entrega Legal (99 mães e 99 recém-nascidos); •	176 pessoas sensibilizadas pelo programa Família Acolhedora, resultando no cadastro e habilitação de 89 famílias e outras 87 famílias em processo de habilitação; •	24.400 visualizações e visitas à página do Programa Família Acolhedora em parceria com a PBH; •	1.982 crianças e adolescentes em situação de acolhimento institucional participantes de atividades diversas, como cineclube promovido pelo TJMG, visitas a museus, teatro, zoológicos, entre outras atividades culturais; •	500 magistrados participantes de Fóruns da Infância e Juventude; •	469 adolescentes com contrato de aprendizagem formalizados no âmbito do Programa Descubra; •	3 adolescentes admitidos por empresas parceiras do Programa Jovens Parceiros, 80 adolescentes iniciaram contrato de aprendizagem em 2025; •	250 participantes, entre parceiros institucionais, crianças e adolescentes acolhidos e em situação de vulnerabilidade social, em ação voltada à proteção de mulheres, crianças e adolescentes, do evento “Praça da Estação” – Projetos "Espaço D'Elas" e "Nascentes"; •	1522 apadrinhamentos sendo 553 afetivos e 533 na modalidade prestador de serviços e 436 na modalidade provedor. •	314 pessoas certificadas pelo webinário Entrega Legal, cerca de 1,9 mil acessos no Youtube; •	503 certificados emitidos no webinário Família Acolhedora – Fluxos e Impasses Jurídicos; •	200 crianças em situação de acolhimento institucional atendidas na Rua de Lazer, evento dia das crianças; •	325 pessoas participantes de evento de apresentação do programa Descubra, resultando na formalização da Assprom e da Junior Achievement como parceiros do Programa e do TJMG como instituição concedente de práticas; •	725 pessoas alcançadas por vídeos do programa “Justiça em Questão” e do “Programa Interlocução” que trataram da edição especial em comemoração ao Dia Nacional da Adoção, da celebração dos 35 anos do Estatuto da Criança e do Adolescente – ECA, além do tema “Escuta protegida de crianças e adolescentes em situação de violência”; •	600 pessoas alcançadas com a publicação do livro “Travessias da Infância e Juventude”; •	99.260 pessoas alcançadas pela realização de campanhas de adoção em estádios de futebol (Cruzeiro x Atlético (18/05) e Atlético x Corinthians (24/05). •	125 certificados do Seminário COINJ/PUC realizado nos dias 20 e 27 de outubro, nas unidades Coração Eucarístico e Barreiro da PUC Minas com os temas “REDE DE PROTEÇÃO DA INFÂNCIA E DA JUVENTUDE” e “SISTEMA SOCIOEDUCATIVO E MEDIDAS DE PROTEÇÃO”; •	278 participantes on-line e 93 participantes ao vivo no Seminário Travessias em Rede: Seminários Regionais da Infância e Juventude.</t>
+          <t>Até dezembro de 2025, 135.419 pessoas foram beneficiadas com ações de impacto social promovidas pela COINJ, sendo: •198 pessoas alcançadas pelo Programa Entrega Legal (99 mães e 99 recém-nascidos); •176 pessoas sensibilizadas pelo programa Família Acolhedora, resultando no cadastro e habilitação de 89 famílias e outras 87 famílias em processo de habilitação; •24.400 visualizações e visitas à página do Programa Família Acolhedora em parceria com a PBH; •1.982 crianças e adolescentes em situação de acolhimento institucional participantes de atividades diversas, como cineclube promovido pelo TJMG, visitas a museus, teatro, zoológicos, entre outras atividades culturais; •500 magistrados participantes de Fóruns da Infância e Juventude; •469 adolescentes com contrato de aprendizagem formalizados no âmbito do Programa Descubra; •3 adolescentes admitidos por empresas parceiras do Programa Jovens Parceiros, 80 adolescentes iniciaram contrato de aprendizagem em 2025; •250 participantes, entre parceiros institucionais, crianças e adolescentes acolhidos e em situação de vulnerabilidade social, em ação voltada à proteção de mulheres, crianças e adolescentes, do evento “Praça da Estação” – Projetos "Espaço D'Elas" e "Nascentes"; •1522 apadrinhamentos sendo 553 afetivos e 533 na modalidade prestador de serviços e 436 na modalidade provedor. •314 pessoas certificadas pelo webinário Entrega Legal, cerca de 1,9 mil acessos no Youtube; •503 certificados emitidos no webinário Família Acolhedora – Fluxos e Impasses Jurídicos; •200 crianças em situação de acolhimento institucional atendidas na Rua de Lazer, evento dia das crianças; •325 pessoas participantes de evento de apresentação do programa Descubra, resultando na formalização da Assprom e da Junior Achievement como parceiros do Programa e do TJMG como instituição concedente de práticas; •725 pessoas alcançadas por vídeos do programa “Justiça em Questão” e do “Programa Interlocução” que trataram da edição especial em comemoração ao Dia Nacional da Adoção, da celebração dos 35 anos do Estatuto da Criança e do Adolescente – ECA, além do tema “Escuta protegida de crianças e adolescentes em situação de violência”; •600 pessoas alcançadas com a publicação do livro “Travessias da Infância e Juventude”; •99.260 pessoas alcançadas pela realização de campanhas de adoção em estádios de futebol (Cruzeiro x Atlético (18/05) e Atlético x Corinthians (24/05). •125 certificados do Seminário COINJ/PUC realizado nos dias 20 e 27 de outubro, nas unidades Coração Eucarístico e Barreiro da PUC Minas com os temas “REDE DE PROTEÇÃO DA INFÂNCIA E DA JUVENTUDE” e “SISTEMA SOCIOEDUCATIVO E MEDIDAS DE PROTEÇÃO”; •278 participantes on-line e 93 participantes ao vivo no Seminário Travessias em Rede: Seminários Regionais da Infância e Juventude.</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Meta TJMG 5 (Julgamentos Monocráticos). Até dezembro de 2025, a meta de realizar 70% dos julgamentos monocráticos em até 60 dias não foi alcançada. O desempenho médio apurado foi de 65%, ficando abaixo do esperado. Segundo o Centro de Resultados da prestação jurisdicional na 2ª Instância (CEINJUR), o desempenho abaixo do esperado pode ser atribuído a fatores como aumento no volume de processos e variações de produtividade causados por férias e recessos e limitações de julgamento. Para garantir o controle dos números e o cumprimento das metas, a 1ºª vice-presidência disponibiliza recursos essenciais, como: painéis Táticos para visualização em tempo real do acervo e produtividade, ferramentas Push com alertas proativos sobre prazos e metas, cursos e treinamentos contínuos para servidores e gestão integrada através da interação constante com os cartórios, o que provou ser a estratégia mais eficaz.</t>
+          <t>Meta TJMG 5 (Julgamentos Monocráticos). Até dezembro de 2025, a meta de realizar 70% dos julgamentos monocráticos em até 60 dias não foi alcançada. O desempenho médio apurado foi de 65%, ficando abaixo do esperado. Segundo o Centro de Resultados da prestação jurisdicional na 2ª Instância (CEINJUR), o desempenho abaixo do esperado pode ser atribuído a fatores como aumento no volume de processos e variações de produtividade causados por férias e recessos e limitações de julgamento. Para garantir o controle dos números e o cumprimento das metas, a 1ª vice-presidência disponibiliza recursos essenciais, como: painéis Táticos para visualização em tempo real do acervo e produtividade, ferramentas Push com alertas proativos sobre prazos e metas, cursos e treinamentos contínuos para servidores e gestão integrada através da interação constante com os cartórios, o que provou ser a estratégia mais eficaz.</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>A meta “TJMG 17” previu a execução, até dezembro de 2025, 70% (setenta por cento) dos marcos previstos para o ano na iniciativa "Plano de estruturação organizacional para a produtividade na prestação jurisdicional". Para 2025, o escopo inicialmente aprovado previu a conclusão de 6 entregas. Entretanto, ao longo do ano, outras 19 entregas foram alinhadas com a Presidência para serem concluídas ainda em 2025, ampliando o universo de análise para um total de 25 entregas previstas para o ano. Até o mês de novembro, 24 delas já haviam sido concluídas, valor que representa um resultado de 96% na meta estabelecida. As entregas concluídas ao longo do ano foram: •Resolução 1088/PR/2025 - “Altera composição das Unidades Jurisdicionais do Sistema dos Juizados Especiais da Comarca de Belo Horizonte e dá outras providências”; •Resolução 1089/PR/2025 - “Altera a denominação e a competência de vara da Comarca de Ribeirão das Neves e dá outras providências”; •Resolução 1090/PR/2025 - “Altera a competência de varas da Comarca de Ipatinga”; •Resolução 1098/PR/2025 - ”Altera a Resolução do Órgão Especial nº 819, de 15 de junho de 2016, que ‘Institui o Sistema de Gerenciamento Matricial de Unidades Judiciárias, no âmbito da Justiça Comum de Primeiro Grau do Estado de Minas Gerais’”; •Resolução 1099/PR/2025 - “Dispõe sobre a desinstalação do Ofício do 3º Tabelionato de Notas da Comarca de Ituiutaba e dá outras providências”; •Resolução 1101/PR/2025  - “Altera a competência de varas da Comarca de São Gotardo e dá outras providências”; •Resolução 1102/PR/2025 - “Altera a denominação e a competência de varas da Comarca de Lavras e dá outras providências”; •Resolução 1104/PR/2025  - “Altera a competência de varas da Comarca de Contagem e dá outras providências”; •Resolução 1105/PR/2025 -  “Altera a denominação e a competência de varas e determina a instalação de vara na Comarca de Uberaba, dispõe sobre a unificação das Secretarias de Juízo das Varas Criminais da referida comarca e dá outras providências”; •Resolução 1107/PR/2025 - “Altera a competência da 1ª, 2ª, 3ª, 4ª e 5ª Varas de Tóxicos, Organização Criminosa e Lavagem de Dinheiro da Comarca de Belo Horizonte e dá outras providências”; •Resolução 1108/2025 - “Dispõe sobre a implantação do Juiz das Garantias, a instalação da 1ª e 2ª Varas das Garantias e a criação e a regulamentação da Central das Garantias da Comarca de Belo Horizonte e dá outras providências”; •Resolução 1112/PR/2025 - ”Dispõe sobre a desinstalação do Ofício do 2º Tabelionato de Notas da Comarca de São João delRei e dá outras providências”; •Resolução 1113/PR/2025 - “Altera a competência da 2ª Vara Cível da Comarca de Belo Horizonte para especializá-la no processo e julgamento das ações afetas ao direito à saúde suplementar”; •Resolução 1114/PR/2025 - ”Dispõe sobre a desinstalação do Ofício do 3º Tabelionato de Notas da Comarca de Sabará e dá outras providências”; •Resolução 1115/PR/2025 - ”Dispõe sobre a organização e o funcionamento da Turma de Uniformização de Jurisprudência, no âmbito dos Juizados Especiais do Estado de Minas Gerais“; •Resolução 1116/PR/2025 - ”Altera a Resolução do Órgão Especial nº 792, de 23 de abril de 2015, que "Dispõe sobre a função de juiz leigo, de que trata a Lei federal nº 9.099, de 26 de setembro de 1995, no âmbito dos Juizados Especiais do Estado de Minas Gerais'“; •Resolução 1117/PR/2025 - ”Dispõe sobre a desinstalação do Ofício do 2º Tabelionato de Notas da Comarca de São João delRei e dá outras providências”; •Resolução 1118/PR/2025 - ”Altera a Resolução do Órgão Especial nº 781, de 4 de dezembro de 2014, que ‘Dispõe sobre a implantação da Turma Recursal, de jurisdição exclusiva, de Belo Horizonte, Betim e Contagem’”; •Resolução 1119/PR/2025 - ”Regulamenta a permuta entre magistrados vinculados ao Tribunal de Justiça do Estado de Minas Gerais e magistrados vinculados a tribunais de justiça de outro Estado Federado ou do Distrito Federal e dos Territórios“; •Resolução 1121/PR/2025  - “Dispõe sobre a elevação da Comarca de Nova Lima para a entrância especial.”; •Resolução 1122/PR/2025 - ”Altera a competência de unidades judiciárias da Comarca de Governador Valadares e dá outras providências”; •Resolução 1123/PR/2025 - ”Altera a competência de varas da Comarca de Uberlândia e dá outras providências”; •Resolução 1126/PR/2025 - ” Dispõe sobre a instalação de serventia extrajudicial no Município e Comarca de São João del-Rei, especifica novas linhas divisórias correspondentes às circunscrições geográficas do 1º e 2º Ofícios de Registro de Imóveis da Comarca de São João del-Rei e dá outras providências”. •Vale ainda ressaltar a aprovação do “Projeto de Lei Complementar (Alteração de Lei Complementar nº 59/2001), que  visando a “Transferência do Município de Laranjal da Comarca de Muriaé para a de Palma”. Após a aprovação do Órgão Especial do TJMG no dia 12/03, a minuta do normativo foi encaminhada para aprovação final da Assembleia Legislativa do Estado de Minas Gerais, não tendo sido, porém, votada até dezembro de 2025. Está pendente apenas a “Elaboração de minuta de Resolução que Dispõe sobre a lotação e o provimento dos cargos de Assessor de Juiz e das funções de confiança de assessoramento da Direção do Foro do Quadro de Cargos de Provimento em Comissão e de Funções de Confiança do Poder Judiciário”. Embora houvesse, inicialmente, a expectativa de que esta fosse publicada ainda em 2025, após a realização de um conjunto de alinhamentos ao longo do ano, verificou-se a necessidade de publicação de um normativo anterior, visando a definição de agrupamentos entre unidades que tem a mesma competência para subsidiar análises estatísticas que orientarão a distribuição dos cargos. As tratativas para a elaboração deste novo normativo estão em andamento, tendo sido iniciadas em novembro de 2025 e com previsão de conclusão em 2026.</t>
+          <t>A meta “TJMG 17” previu a execução, até dezembro de 2025, de 70% (setenta por cento) dos marcos previstos para o ano na iniciativa "Plano de estruturação organizacional para a produtividade na prestação jurisdicional". O escopo inicialmente aprovado previu a conclusão de 6 entregas. Entretanto, ao longo do ano, outras 19 entregas foram alinhadas com a Presidência para serem concluídas ainda em 2025, ampliando o universo de análise para um total de 25 entregas previstas para o ano. Até o mês de novembro, 24 delas já haviam sido concluídas, valor que representa um resultado de 96% na meta estabelecida. As entregas concluídas ao longo do ano foram: •Resolução 1088/PR/2025 - “Altera composição das Unidades Jurisdicionais do Sistema dos Juizados Especiais da Comarca de Belo Horizonte e dá outras providências”; •Resolução 1089/PR/2025 - “Altera a denominação e a competência de vara da Comarca de Ribeirão das Neves e dá outras providências”; •Resolução 1090/PR/2025 - “Altera a competência de varas da Comarca de Ipatinga”; •Resolução 1098/PR/2025 - “Altera a Resolução do Órgão Especial nº 819, de 15 de junho de 2016, que ‘Institui o Sistema de Gerenciamento Matricial de Unidades Judiciárias, no âmbito da Justiça Comum de Primeiro Grau do Estado de Minas Gerais’”; •Resolução 1099/PR/2025 - “Dispõe sobre a desinstalação do Ofício do 3º Tabelionato de Notas da Comarca de Ituiutaba e dá outras providências”; •Resolução 1101/PR/2025  - “Altera a competência de varas da Comarca de São Gotardo e dá outras providências”; •Resolução 1102/PR/2025 - “Altera a denominação e a competência de varas da Comarca de Lavras e dá outras providências”; •Resolução 1104/PR/2025  - “Altera a competência de varas da Comarca de Contagem e dá outras providências”; •Resolução 1105/PR/2025 -  “Altera a denominação e a competência de varas e determina a instalação de vara na Comarca de Uberaba, dispõe sobre a unificação das Secretarias de Juízo das Varas Criminais da referida comarca e dá outras providências”; •Resolução 1107/PR/2025 - “Altera a competência da 1ª, 2ª, 3ª, 4ª e 5ª Varas de Tóxicos, Organização Criminosa e Lavagem de Dinheiro da Comarca de Belo Horizonte e dá outras providências”; •Resolução 1108/2025 - “Dispõe sobre a implantação do Juiz das Garantias, a instalação da 1ª e 2ª Varas das Garantias e a criação e a regulamentação da Central das Garantias da Comarca de Belo Horizonte e dá outras providências”; •Resolução 1112/PR/2025 - “Dispõe sobre a desinstalação do Ofício do 2º Tabelionato de Notas da Comarca de São João delRei e dá outras providências”; •Resolução 1113/PR/2025 - “Altera a competência da 2ª Vara Cível da Comarca de Belo Horizonte para especializá-la no processo e julgamento das ações afetas ao direito à saúde suplementar”; •Resolução 1114/PR/2025 - “Dispõe sobre a desinstalação do Ofício do 3º Tabelionato de Notas da Comarca de Sabará e dá outras providências”; •Resolução 1115/PR/2025 - “Dispõe sobre a organização e o funcionamento da Turma de Uniformização de Jurisprudência, no âmbito dos Juizados Especiais do Estado de Minas Gerais”; •Resolução 1116/PR/2025 - “Altera a Resolução do Órgão Especial nº 792, de 23 de abril de 2015, que ‘Dispõe sobre a função de juiz leigo, de que trata a Lei federal nº 9.099, de 26 de setembro de 1995, no âmbito dos Juizados Especiais do Estado de Minas Gerais’”; •Resolução 1117/PR/2025 - “Dispõe sobre a desinstalação do Ofício do 2º Tabelionato de Notas da Comarca de São João delRei e dá outras providências”; •Resolução 1118/PR/2025 - “Altera a Resolução do Órgão Especial nº 781, de 4 de dezembro de 2014, que ‘Dispõe sobre a implantação da Turma Recursal, de jurisdição exclusiva, de Belo Horizonte, Betim e Contagem’”; •Resolução 1119/PR/2025 - “Regulamenta a permuta entre magistrados vinculados ao Tribunal de Justiça do Estado de Minas Gerais e magistrados vinculados a tribunais de justiça de outro Estado Federado ou do Distrito Federal e dos Territórios“; •Resolução 1121/PR/2025  - “Dispõe sobre a elevação da Comarca de Nova Lima para a entrância especial.”; •Resolução 1122/PR/2025 - “Altera a competência de unidades judiciárias da Comarca de Governador Valadares e dá outras providências”; •Resolução 1123/PR/2025 - “Altera a competência de varas da Comarca de Uberlândia e dá outras providências”; •Resolução 1126/PR/2025 - “Dispõe sobre a instalação de serventia extrajudicial no Município e Comarca de São João del-Rei, especifica novas linhas divisórias correspondentes às circunscrições geográficas do 1º e 2º Ofícios de Registro de Imóveis da Comarca de São João del-Rei e dá outras providências”. Vale ainda ressaltar a aprovação do “Projeto de Lei Complementar (Alteração de Lei Complementar nº 59/2001), visando a ‘Transferência do Município de Laranjal da Comarca de Muriaé para a de Palma’”. Após a aprovação do Órgão Especial do TJMG no dia 12/03, a minuta do normativo foi encaminhada para aprovação final da Assembleia Legislativa do Estado de Minas Gerais, não tendo sido, porém, votada até dezembro de 2025. Está pendente apenas a “Elaboração de minuta de Resolução que Dispõe sobre a lotação e o provimento dos cargos de Assessor de Juiz e das funções de confiança de assessoramento da Direção do Foro do Quadro de Cargos de Provimento em Comissão e de Funções de Confiança do Poder Judiciário”. Embora houvesse, inicialmente, a expectativa de que esta fosse publicada ainda em 2025, após a realização de um conjunto de alinhamentos ao longo do ano, verificou-se a necessidade de publicação de um normativo anterior, visando a definição de agrupamentos entre unidades que tem a mesma competência para subsidiar análises estatísticas que orientarão a distribuição dos cargos. As tratativas para a elaboração deste novo normativo estão em andamento, tendo sido iniciadas em novembro de 2025 e com previsão de conclusão em 2026.</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Em relação à Meta TJMG 115 -   Devolver para o respectivo Cartório 95% (noventa e cinco por cento) dos processos conclusos no prazo de até 90 (noventa) dias, contado da data da conclusão, o resultado médio apurado até dezembro de 2025 é de 94%. O resutlado muito próximo da meta é devido ao desempenho da Secretaria Judiciária na gestão dos prazos, atuando de forma proativa para estimular a devolução célere dos processos conclusos e orientar gabinetes e cartórios quanto á melhores práticas</t>
+          <t>Em relação à Meta TJMG 115 -   Devolver para o respectivo Cartório 95% (noventa e cinco por cento) dos processos conclusos no prazo de até 90 (noventa) dias, contado da data da conclusão, o resultado médio apurado até dezembro de 2025 é de 94%. O resultado muito próximo da meta é devido ao desempenho da Secretaria Judiciária na gestão dos prazos, atuando de forma proativa para estimular a devolução célere dos processos conclusos e orientar gabinetes e cartórios quanto á melhores práticas.</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Desde junho de 2024 até dezembro de 2025, já foram cessadas as competências delegada em 64 Comarcas, elencadas a seguir, representando o alcance da meta de 2025. 2024 (26 comarcas): •18 comarcas em decorrência do institucionalização do entendimento de que a UAA é funcionalmente equivalente a uma vara e declarou-se cessada a competência delegada Águas Formosas; Almenara; Araçuaí; Capelinha; Carangola; Carlos Chagas; Corinto; Curvelo; Diamantina; Jacinto; Jequitinhonha; Malacacheta; Medina; Mutum; Nanuque; Novo Cruzeiro; Pedra Azul e Serro; •1 comarcas em decorrência instalada em Comarcas do TJMG - projeto piloto: Patrocínio; e •7 comarcas em decorrência de parcerias com municípios (Prefeituras): Araguari, Barão de Cocais, Divino, Estrela do Sul, Itabira, Santa Bárbara e Tupaciguara. 2025 (38 comarcas): •30 comarcas em decorrência instalada em Comarcas do TJMG: Monte Carmelo, Nova Ponte, Minas Novas, Turmalina, Januária, Manga, Montalvânia, Boa Esperança, Candeias, Taiobeiras, Rio Pardo de Minas, São João do Paraíso, João Pinheiro, Coração de Jesus, Brasília de Minas,  Baependi, Aiuruoca, Caxambu, Conceição do Rio Verde, Cruzília, Abaeté, Pompéu, Martinho Campos, Lambari, Carmo de Minas, Cristina, Natércia, Pedralva, São Lourenço e Caratinga, e •8 comarcas em decorrência de parcerias com municípios (Prefeituras):  Guaxupé, Monte Belo, Muzambinho, Arcos, Formiga, Lagoa da Prata, Iguatama e Bambuí.</t>
+          <t>Desde junho de 2024 até dezembro de 2025, já foram cessadas as competências delegada em 64 Comarcas, elencadas a seguir, representando o alcance da meta de 2025. 2024 (26 comarcas): •18 comarcas em decorrência da institucionalização do entendimento de que a UAA é funcionalmente equivalente a uma vara e declarou-se cessada a competência delegada de Águas Formosas; Almenara; Araçuaí; Capelinha; Carangola; Carlos Chagas; Corinto; Curvelo; Diamantina; Jacinto; Jequitinhonha; Malacacheta; Medina; Mutum; Nanuque; Novo Cruzeiro; Pedra Azul e Serro; •1 comarcas em decorrência instalada em Comarcas do TJMG - projeto piloto: Patrocínio; e •7 comarcas em decorrência de parcerias com municípios (Prefeituras): Araguari, Barão de Cocais, Divino, Estrela do Sul, Itabira, Santa Bárbara e Tupaciguara. 2025 (38 comarcas): •30 comarcas em decorrência instalada em Comarcas do TJMG: Monte Carmelo, Nova Ponte, Minas Novas, Turmalina, Januária, Manga, Montalvânia, Boa Esperança, Candeias, Taiobeiras, Rio Pardo de Minas, São João do Paraíso, João Pinheiro, Coração de Jesus, Brasília de Minas,  Baependi, Aiuruoca, Caxambu, Conceição do Rio Verde, Cruzília, Abaeté, Pompéu, Martinho Campos, Lambari, Carmo de Minas, Cristina, Natércia, Pedralva, São Lourenço e Caratinga, e •8 comarcas em decorrência de parcerias com municípios (Prefeituras):  Guaxupé, Monte Belo, Muzambinho, Arcos, Formiga, Lagoa da Prata, Iguatama e Bambuí.</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Durante a estruturação do Planejamento Estratégico para 2025, a meta estratégica TJMG 133 previu “Instalar, em 2025, o eproc nas demais unidades da justiça comum e especial com competência cível do Município de Belo Horizonte, incluindo a Turma Recursal Temporária de Belo Horizonte, Betim e Contagem, bem como nas Câmaras do Tribunal de Justiça com competências  originárias da Segunda Instância (Mandado de Segurança, Rescisória e Reclamação), relativas ao Direito Público e Privado”. Entretanto, o cronograma dos ciclos de expansão previstos para o ano - os quais foram estabelecidos por meio da publicação das portarias: Portaria Conjunta nº 1.635/PR/2025 (1° ciclo); Portaria Conjunta nº 1.645/PR/2025 (2º Ciclo); Portaria Conjunta nº 1.659/PR/2025  (3º Ciclo); Portaria Conjunta nº 1.668/PR/2025 (4º Ciclo), e; Portaria Conjunta nº 1.710/PR/2025 (5º Ciclo) - considerou, além das unidades judiciárias com competência cível de Belo Horizonte, o tratamento de competências e atos em específicos, ampliando o universo de trabalho inicialmente previsto. Nesse sentido, como forma melhor comunicar o trabalho realizado ao longo do ano, propõe-se a alteração da meta aprovada para “concluir, em 2025, 100% dos ciclos de expansão previstos para a instalação do sistema eproc nas demais unidades da justiça comum e especial, com competência cível, do município de Belo Horizonte, incluindo a Turma Recursal Temporária de Belo Horizonte, Betim e Contagem, bem como nas Câmaras do Tribunal de Justiça com competências originárias da segunda instância, Mandado de Segurança, Rescisória e Reclamações, relativas ao Direito Público e Privado”. Até setembro de 2025, os cincos ciclos de expansão previsto para o ano foram concluídos, de modo que o resultado apurado da nova meta proposta é de 100%.</t>
+          <t>A meta estratégica TJMG 133 previu “Instalar, em 2025, o eproc nas demais unidades da justiça comum e especial com competência cível do Município de Belo Horizonte, incluindo a Turma Recursal Temporária de Belo Horizonte, Betim e Contagem, bem como nas Câmaras do Tribunal de Justiça com competências  originárias da Segunda Instância (Mandado de Segurança, Rescisória e Reclamação), relativas ao Direito Público e Privado”. Entretanto, o cronograma dos ciclos de expansão previstos para o ano - os quais foram estabelecidos por meio da publicação das portarias: Portaria Conjunta nº 1.635/PR/2025 (1° ciclo); Portaria Conjunta nº 1.645/PR/2025 (2º Ciclo); Portaria Conjunta nº 1.659/PR/2025  (3º Ciclo); Portaria Conjunta nº 1.668/PR/2025 (4º Ciclo), e; Portaria Conjunta nº 1.710/PR/2025 (5º Ciclo) - considerou, além das unidades judiciárias com competência cível de Belo Horizonte, o tratamento de competências e atos em específicos, ampliando o universo de trabalho inicialmente previsto. Nesse sentido, como forma de melhor comunicar o trabalho realizado ao longo do ano, propõe-se a alteração da meta aprovada para “concluir, em 2025, 100% dos ciclos de expansão previstos para a instalação do sistema eproc nas demais unidades da justiça comum e especial, com competência cível, do município de Belo Horizonte, incluindo a Turma Recursal Temporária de Belo Horizonte, Betim e Contagem, bem como nas Câmaras do Tribunal de Justiça com competências originárias da segunda instância, Mandado de Segurança, Rescisória e Reclamações, relativas ao Direito Público e Privado”. Até setembro de 2025, os cincos ciclos de expansão previsto para o ano foram concluídos, de modo que o resultado apurado da nova meta proposta é de 100%.</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>A meta TJMG 156 foi estabelecida após a publicação da Portaria Conjunta n° 1.681/2025, que previu que a expansão para do Sistema eproc para as comarcas com competência cível lato sensu do interior do estado de Minas Gerais seria conduzida em 5 ciclos de implantação, como forma de contemplar as 297 comarcas que ainda não receberam o sistema. O resultado da meta é dado a partir do somatório do total de comarcas contempladas em cada ciclo. Até novembro de 2025, conforme o cronograma estipulado pela própria Portaria, 2 ciclos de expansão já foram concluídos, contemplando um total de 84 comarcas: 39 no 1° ciclo e 45 no 2° ciclo. Nesse sentido, a meta estipulada foi alcançada. Para o ano de 2026, estão ainda previstos 3 ciclos de expansão, que buscarão contemplar as demais 213 comarcas restantes.</t>
+          <t>A Meta TJMG 156, aprovada em outubro pelo Comitê de Governança e Gestão Estratégica, foi estabelecida após a publicação da Portaria Conjunta n° 1.681/2025, que previu que a expansão do Sistema eproc para as comarcas com competência cível lato sensu do interior do estado de Minas Gerais seria conduzida em 5 ciclos de implantação, como forma de contemplar as 297 comarcas que ainda não receberam o sistema. Até novembro de 2025, conforme o cronograma estipulado pela própria Portaria, 2 ciclos de expansão já foram concluídos, contemplando um total de 84 comarcas: 39 no 1° ciclo e 45 no 2° ciclo. Nesse sentido, a meta estipulada foi alcançada. Para o ano de 2026, estão ainda previstos 3 ciclos de expansão, que buscarão contemplar as demais 213 comarcas restantes</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>O resultado apurado corresponde a 0%. Isso ocorreu porque nos meses de janeiro, fevereiro, abril, maio, junho, julho, agosto, setembro, outubro, novembro e dezembro, houve julgamento de mérito, porém, todos eles superiores a 320 dias. E, no mês de março, não houve julgamento do mérito. Diante desse resultado e, para auxiliar as sessões cujas atribuições envolvem julgar os Incidentes de Resolução de Demandas Repetitivas (IRDR) e os Incidentes de Assunção de Competência (IAC), a Primeira Vice-Presidência do Tribunal de Justiça de Minas Gerais,  por meio do Núcleo de Gerenciamento de Precedentes (NUGEPNAC) elaborou e apresentou aos desembargadores envolvidos o Projeto de Aperfeiçoamento na Formação de Precedentes cujo objetivo é fortalecer a segurança jurídica, garantir a isonomia nas decisões, a previsibilidade e coerência dos entendimentos firmados, acelerar a prestação jurisdicional, garantir a clareza das teses firmadas e preservar a unidade e integridade do nosso sistema de justiça. O ponto importante desse projeto é:  para otimizar essa colaboração, cada Desembargador(a) membro das Seções poderá indicar um assessor para ser o contato direto com o NUGEPNAC, e para ser treinado como multiplicador. A intenção é fazer um nivelamento e municiar as assessorias com informações cruciais para o bom andamento dos incidentes em tramitação e para o alcance das metas do Planejamento Estratégico.</t>
+          <t>O resultado apurado corresponde a 0%. Embora tenham ocorrido julgamentos de mérito em todos os meses do ano, exceto em março, todos os processos foram concluídos após o prazo estipulado de 320 dias. Diante desse resultado e, para auxiliar as sessões cujas atribuições envolvem julgar os Incidentes de Resolução de Demandas Repetitivas (IRDR) e os Incidentes de Assunção de Competência (IAC), a Primeira Vice-Presidência do Tribunal de Justiça de Minas Gerais,  por meio do Núcleo de Gerenciamento de Precedentes (NUGEPNAC) elaborou e apresentou aos desembargadores envolvidos o Projeto de Aperfeiçoamento na Formação de Precedentes cujo objetivo é fortalecer a segurança jurídica, garantir a isonomia nas decisões, a previsibilidade e coerência dos entendimentos firmados, acelerar a prestação jurisdicional, garantir a clareza das teses firmadas e preservar a unidade e integridade do nosso sistema de justiça. O ponto importante desse projeto é:  para otimizar essa colaboração, cada Desembargador(a) membro das Seções poderá indicar um assessor para ser o contato direto com o NUGEPNAC, e para ser treinado como multiplicador. A intenção é fazer um nivelamento e municiar as assessorias com informações cruciais para o bom andamento dos incidentes em tramitação e para o alcance das metas do Planejamento Estratégico.</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O resultado apurado corresponde a 0%. Nos meses de janeiro, fevereiro, março, maio, junho, julho, setembro, outubro, novembro e dezembro, houve julgamento de mérito, porém todos superiores a 150 dias.  E, nos meses de abril e agosto não houve julgamento do mérito. Diante desse resultado e, para auxiliar as sessões cujas atribuições envolvem julgar os Incidentes de Resolução de Demandas Repetitivas (IRDR) e os Incidentes de Assunção de Competência (IAC), a Primeira Vice-Presidência do Tribunal de Justiça de Minas Gerais,  por meio do Núcleo de Gerenciamento de Precedentes (NUGEPNAC) elaborou e apresentou aos desembargadores envolvidos o Projeto de Aperfeiçoamento na Formação de Precedentes cujo objetivo é fortalecer a segurança jurídica, garantir a isonomia nas decisões, a previsibilidade e coerência dos entendimentos firmados, acelerar a prestação jurisdicional, garantir a clareza das teses firmadas e preservar a unidade e integridade do nosso sistema de justiça. O ponto importante desse projeto é:  para otimizar essa colaboração, cada Desembargador(a) membro das Seções poderá indicar um assessor para ser o contato direto com o NUGEPNAC, e para ser treinado como multiplicador. A intenção é fazer um nivelamento e municiar as assessorias com informações cruciais para o bom andamento dos incidentes em tramitação e para o alcance das metas do Planejamento Estratégico.</t>
+          <t>O resultado apurado corresponde a 0%. Ocorreram julgamentos de mérito em todos os meses do ano, com exceção de abril e agosto, no entanto, todos após o prazo de 150 dias. Diante desse resultado e, para auxiliar as sessões cujas atribuições envolvem julgar os Incidentes de Resolução de Demandas Repetitivas (IRDR) e os Incidentes de Assunção de Competência (IAC), a Primeira Vice-Presidência do Tribunal de Justiça de Minas Gerais,  por meio do Núcleo de Gerenciamento de Precedentes (NUGEPNAC) elaborou e apresentou aos desembargadores envolvidos o Projeto de Aperfeiçoamento na Formação de Precedentes cujo objetivo é fortalecer a segurança jurídica, garantir a isonomia nas decisões, a previsibilidade e coerência dos entendimentos firmados, acelerar a prestação jurisdicional, garantir a clareza das teses firmadas e preservar a unidade e integridade do nosso sistema de justiça. O ponto importante desse projeto é:  para otimizar essa colaboração, cada Desembargador(a) membro das Seções poderá indicar um assessor para ser o contato direto com o NUGEPNAC, e para ser treinado como multiplicador. A intenção é fazer um nivelamento e municiar as assessorias com informações cruciais para o bom andamento dos incidentes em tramitação e para o alcance das metas do Planejamento Estratégico.</t>
         </is>
       </c>
     </row>
@@ -2459,16 +2459,12 @@
           <t>Maior – melhor</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>IE 43</t>
@@ -2476,7 +2472,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>A meta da iniciativa 43 - Programa INOVA TJMG é cumprir até dezembro de 2025, 100% das entregas previstas para o ano de 2025 Das 18 entregas previstas para 2025, 2 (duas) entregas foram canceladas, e 16 (dezesseis) entregas foram concluídas. O que representa o valor apurado de 100% até 10/12/2025. As entregas realizadas foram: •23 iniciativas agraciadas com o Certificado Agenda 2030; •Lançamento da cartilha ‘Você não está sozinha’ para o combate à Violência Doméstica; •Lançamento da cartilha ‘Conectando você à Justiça’, dos Fóruns Digitais; •Desenvolvimento de automações e de protótipos de I.A para aprimorar a eficiência operacional e apoiar os magistrados, os colaboradores e os servidores no fluxo de suas atividades diárias; •Oficina de Inovação para Comissão de Assédio; •Oficina de Linguagem Simples e Direito Visual para complementar curso EAD. •Oficina de Linguagem Simples e Direito Visual para Semana Nacional dos Juizados - "Pensar, Criar e Simplificar"; •Oficina de Linguagem Simples e Direito Visual para o Curso de Formação Inicial – CFI; •Desenvolvido o ‘Glossário de Termos Jurídicos’ em Linguagem Simples para utilização no portal do TJMG; •Elaborado o ‘Guia de como utilizar o Juizado Especial’ em Linguagem Simples e Direito Visual; •Elaborado o ‘Guia de Orientações para a Audiência Virtual’ em Linguagem Simples e Direito Visual; e •Realizado o evento Festilabs na Região Sudeste.</t>
+          <t>A meta da iniciativa 43 - Programa INOVA TJMG é cumprir até dezembro de 2025, 100% das entregas previstas para o ano de 2025 Das 18 entregas previstas para 2025, 1 (uma) entrega foi cancelada e 17 (dezessete) entregas foram concluídas. O que representa o valor apurado de 100% até 10/12/2025. As entregas realizadas foram: •23 iniciativas agraciadas com o Certificado Agenda 2030; •Lançamento da cartilha ‘Você não está sozinha’ para o combate à Violência Doméstica; •Lançamento da cartilha ‘Conectando você à Justiça’, dos Fóruns Digitais; •Desenvolvimento de automações e de protótipos de I.A para aprimorar a eficiência operacional e apoiar os magistrados, os colaboradores e os servidores no fluxo de suas atividades diárias; •Oficina de Inovação para Comissão de Assédio; •Oficina de Linguagem Simples e Direito Visual para complementar curso EAD. •Oficina de Linguagem Simples e Direito Visual para Semana Nacional dos Juizados - "Pensar, Criar e Simplificar"; •Oficina de Linguagem Simples e Direito Visual para o Curso de Formação Inicial – CFI; •Desenvolvido o ‘Glossário de Termos Jurídicos’ em Linguagem Simples para utilização no portal do TJMG; •Elaborado o ‘Guia de como utilizar o Juizado Especial’ em Linguagem Simples e Direito Visual; •Elaborado o ‘Guia de Orientações para a Audiência Virtual’ em Linguagem Simples e Direito Visual; e •Realizado o evento Festilabs na Região Sudeste.</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2572,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>A meta  da iniciativa 75 – Ampliação da Eficácia da Sistemática dos Precedentes Qualificados é executar, em 2025, 100% das atividades previstas para o ano. Das 29 atividades previstas para o ano de 2025, 27 foram concluídas, o que corresponde ao valor apurado de 93% ate´dezembro de 2025. As atividades concluídas são: Oferta do curso de Precedentes – Juízes leigos e servidores. Ao final, o curso obteve 191 aprovados. Oferta do curso de treinamento para Escrivães e Escreventes - Gestão de Processos Sobrestados. Na qual participaram da formação, aproximadamente, 25 gestores de cartórios Cíveis e Criminais. Desenvolvida pelo TJMG, a ferramenta automatizada de identificação de precedentes potencialmente aplicáveis ao processo em análise, agilizando a análise dos recursos e promovendo maior uniformização e segurança jurídica nas decisões. A implantação ocorreu em ondas, sendo:  a 1ª onda contemplou as seguintes comarcas: Divinópolis, Santa Luzia, Contagem, Sete Lagoas, Vespasiano, Ibirité e Pará de Minas, com um total de 783 máquinas adaptadas. Já na 2ª onda a implantação da ferramenta contemplou as comarcas de Betim, Ribeirão das Neves, Ubá, Pouso Alegre, Varginha e Poços de Caldas (Fórum), Poços de Caldas (Jesp), com um total de 687 máquinas adaptadas e a 3ª onda nas comarcas de Juiz de Fora (Fórum e JESP), Barbacena, São João Del- Rei, Manhuaçu, Uberlândia, Uberaba e Patos de Minas, com um total de 2055 máquinas adaptadas. Concluída também a implantação da 4ª onda nas comarcas de Caratinga, Ipatinga, Coronel Fabriciano, Timóteo, Itabira, Conselheiro Lafaiete, Governador Valadares, Montes Claros e Teófilo Otoni. Na 5ª onda as comarcas contempladas foram: Jaboticatuba, Juatuba, Alto Rio Doce, Barroso, Bicas, Carandaí, Divino, Ervália e Espera Feliz, com um total de 215 máquinas adaptadas. Na 6ª onda as comarcas contempladas foram: Eugenópolis, Guarani, Jequeri, Lajinha, Lima Duarte, Mas de Espanha, Matias Barbosa, Mercês e Miradouro, com 187 máquinas adaptadas. A 7ª onda contemplou as seguintes comarcas: Miraí, Palma, Piranga, Pirapetinga, Raul Soares, Resende Costa, Rio Casca, Rio Novo, Rio Pomba. Com 167 máquinas adaptadas. Na 8ª onda as comarcas contempladas foram: Rio Preto, Senador Firmino, Teixeiras, Tombos, Aiuroca, Alpinópolis, Andrelândia, Areado e Baependi. Na 9ª onda as comarcas contempladas foram: Bambuí, Bom Sucesso, Borda da Mata, Botelhos, Brazópolis, Bueno Brandão, Cabo Verde, Cachoeira de Minas e Caldas, com 178 máquinas adaptadas, para além da comarca de belo Horizonte com 106 máquinas adaptadas. Já na 10ª onda, foram 202 máquina adaptadas, contemplando as seguintes comarcas: Carmópolis de Minas, Caxambu, Cláudio, Conceição do Rio Verde, Cristina, Cruzília, Elói Mendes, Guapé e Guaranésia. Apresentado aos desembargadores e assessores indicados o conteúdo para ação de nivelamento da ação de Aperfeiçoamento na formação de precedentes - IRDR e IAC. Após elaboração da proposta de Gestão de Incidentes de Uniformização de Jurisprudência - IUJs, a mesma foi apresentada ao 1º Vice Presidente. Publicada a cartilha Ferramentas de Identificação Automática de Precedentes Qualificados, elaborada pela COAPE para orientar adequadamente os usuários do sistema.</t>
+          <t>A meta da iniciativa 75 – Ampliação da Eficácia da Sistemática dos Precedentes Qualificados é executar, em 2025, 100% das atividades previstas para o ano. Das 29 atividades previstas para o ano de 2025, 27 foram concluídas, o que corresponde ao valor apurado de 93% até dezembro de 2025. As atividades concluídas são: Oferta do curso de Precedentes – Juízes leigos e servidores. Ao final, o curso obteve 191 aprovados. Oferta do curso de treinamento para Escrivães e Escreventes - Gestão de Processos Sobrestados. Na qual participaram da formação, aproximadamente, 25 gestores de cartórios Cíveis e Criminais. Desenvolvida pelo TJMG, a ferramenta automatizada de identificação de precedentes potencialmente aplicáveis ao processo em análise, agilizando a análise dos recursos e promovendo maior uniformização e segurança jurídica nas decisões. A implantação ocorreu em ondas, sendo:  a 1ª onda contemplou as seguintes comarcas: Divinópolis, Santa Luzia, Contagem, Sete Lagoas, Vespasiano, Ibirité e Pará de Minas, com um total de 783 máquinas adaptadas. Já na 2ª onda a implantação da ferramenta contemplou as comarcas de Betim, Ribeirão das Neves, Ubá, Pouso Alegre, Varginha e Poços de Caldas (Fórum), Poços de Caldas (Jesp), com um total de 687 máquinas adaptadas e a 3ª onda nas comarcas de Juiz de Fora (Fórum e JESP), Barbacena, São João Del- Rei, Manhuaçu, Uberlândia, Uberaba e Patos de Minas, com um total de 2055 máquinas adaptadas. Concluída também a implantação da 4ª onda nas comarcas de Caratinga, Ipatinga, Coronel Fabriciano, Timóteo, Itabira, Conselheiro Lafaiete, Governador Valadares, Montes Claros e Teófilo Otoni. Na 5ª onda as comarcas contempladas foram: Jaboticatuba, Juatuba, Alto Rio Doce, Barroso, Bicas, Carandaí, Divino, Ervália e Espera Feliz, com um total de 215 máquinas adaptadas. Na 6ª onda as comarcas contempladas foram: Eugenópolis, Guarani, Jequeri, Lajinha, Lima Duarte, Mas de Espanha, Matias Barbosa, Mercês e Miradouro, com 187 máquinas adaptadas. A 7ª onda contemplou as seguintes comarcas: Miraí, Palma, Piranga, Pirapetinga, Raul Soares, Resende Costa, Rio Casca, Rio Novo, Rio Pomba. Com 167 máquinas adaptadas. Na 8ª onda as comarcas contempladas foram: Rio Preto, Senador Firmino, Teixeiras, Tombos, Aiuroca, Alpinópolis, Andrelândia, Areado e Baependi. Na 9ª onda as comarcas contempladas foram: Bambuí, Bom Sucesso, Borda da Mata, Botelhos, Brazópolis, Bueno Brandão, Cabo Verde, Cachoeira de Minas e Caldas, com 178 máquinas adaptadas, para além da comarca de belo Horizonte com 106 máquinas adaptadas. Já na 10ª onda, foram 202 máquina adaptadas, contemplando as seguintes comarcas: Carmópolis de Minas, Caxambu, Cláudio, Conceição do Rio Verde, Cristina, Cruzília, Elói Mendes, Guapé e Guaranésia. Apresentado aos desembargadores e assessores indicados o conteúdo para ação de nivelamento da ação de Aperfeiçoamento na formação de precedentes - IRDR e IAC. Após elaboração da proposta de Gestão de Incidentes de Uniformização de Jurisprudência - IUJs, a mesma foi apresentada ao 1º Vice Presidente. Publicada a cartilha Ferramentas de Identificação Automática de Precedentes Qualificados, elaborada pela COAPE para orientar adequadamente os usuários do sistema.</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2672,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Verifica-se que, até dezembro de 2025, foram concluídas 26 entregas das 31 prevista para o Programa, sendo 6 em 2023, 13 em 2024 e 7 em 2025, obtendo um resultado apurado de 87,39%. As entregas concluídas em 2025, são: Implantação dos equipamentos Audiovisuais e TIC no Auditório do Juizado Especial Cível Implantação dos equipamentos Audiovisuais e TIC no Auditório do Pleno (ed. Sede). Implantação de VideoWall – Auditório do Pleno. Implantação do Projeto Piloto para transmissão ao vivo (streaming) das Sessões de Julgamento do Órgão Especial, utilizando a Plataforma Youtube. Implantação e gerenciamento de Equipe Técnica para operacionalização dos novos equipamentos de áudio e TIC. Implantação do Software de Videoconferência. Implantação do Sistema de Emenda Regimental. Além dessas, 1 entrega foi cancelada, 1 não iniciada e 3 estão em andamento, com perspectiva de conclusão em 2026. A entrega Fluxos de trabalho decorrentes das novas tecnologias do Programa foi cancelada porque não será mais realizada nos termos em que foi planejada. Inicialmente, foi previsto que o CEPROC (Centro de Gestão de Processos de Trabalho, Padronização e Qualidade) redesenharia todos os processos de trabalho que, eventualmente, sofressem alteração em decorrência das melhorias tecnológicas implementadas para modernização dos plenários. No entanto, na prática, o que se verifica é uma atuação mais direcionada para áreas que demandam o serviço. Cabe ressaltar que a entrega, quando cancelada, não impacta o cumprimento da meta em questão. O projeto piloto para a transmissão ao vivo (Streaming) das Sessões de Julgamento no TJMG, foi considerado concluído em 13/08, com a primeira gravação da sessão do Órgão especial. As sessões do Órgão Especial passaram a ser integralmente transmitidas pelo canal oficial do TJMG no YouTube a partir de 10 de setembro de 2025, sendo vedada a transmissão de pautas submetidas a segredo de justiça. Com isso, o TJMG passa a cumprir os itens 12 e 13 constantes no Anexo da Portaria nº 406 do Conselho Nacional de justiça (CNJ) de 29 de novembro de 2024, que estabelece o regulamento do Ranking da Transparência do Poder Judiciário – 2025. A entrega Implantação da Plataforma Youtube para transmissão ao vivo (Streaming) das Sessões de julgamento, que prevê a expansão da transmissão ao vivo para as sessões dos plenários, foi impactada pelo atraso do piloto, ficando suspensa ao longo de 2025. Além disso, para expansão, aguardava-se a definição da Alta Administração quanto a estratégia para a expansão (data, ordem dos Plenários, etc.). Contudo, recentemente, deliberou -se sobre a retomada da expansão das transmissões, motivo pelo qual a entrega possui perspectiva de conclusão em 2026. No que tange às entregas em andamento: Em 2023, o processo licitatório para a aquisição do sistema para votação administrativa foi deserto. Diante disso, deliberou-se por promover melhorias no módulo SEI Julgar para viabilizar a sua utilização pelo TJMG. Embora algumas customizações já tenham sido realizadas ao longo de 2024 e 2025, ainda restam funcionalidades a serem desenvolvidas, sem as quais não é possível realizar o projeto piloto.  A entrega ficou suspensa ao longo de 2025, tendo em vista que a equipe técnica responsável pelo desenvolvimento estava alocada em outras frentes de trabalho igualmente relevantes para instituição. Estima-se a retomada da customização do sistema para votação administrativa para 2026. Por meio de Acordo de Cooperação (AC) com o TRF-4, houve a cessão do software Tela para Gravação e Indexação das sessões do TJMG. Ele foi implantado inicialmente nos plenários 4 e 10. Atualmente, o projeto encontra-se em fase de adaptações e aprimoramento entre o Sistema TELA e o Eproc, com previsão de início da expansão para os demais plenários entre fevereiro e março de 2026. Em relação à transcrição, o projeto-piloto da implantação da 'Solução de Transposição' da empresa Xértica nos plenários 4 e 10, em setembro de 2025, foi bem-sucedido. Assim sendo, o início da expansão para as demais unidades está previsto para fevereiro de 2026. O início da expansão para o Auditório está condicionado à implementação prévia de melhorias e adaptações estruturais de longo prazo no sistema TELA, conforme demanda da área de negócio. Em razão da necessidade desses ajustes técnicos, ainda não há data definida para a conclusão desta etapa, a qual será estabelecida após a entrega das adequações mencionadas. Ainda sobre a entrega software Tela para Gravação, Indexação e Transcrição das sessões, cabe ressaltar que o módulo de Gestão de Pedidos vai permitir a gestão dos pedidos de acesso à informação de gravação e transcrição das sessões de julgamento feitos pelo Desembargador demandante. Esclarece-se que essa sistemática já existe dentro do Themis, mas, tendo em vista que esse sistema será descontinuado, foi deliberada a utilização do E-proc para o mesmo fim.  Para tanto, serão necessários ajustes no E-proc, visando tanto a integração com o Tela quanto o desenvolvimento/adequações de funcionalidades atinentes ao módulo de gestão de pedidos, que começarão a ser realizados após a conclusão da homologação do sistema Tela. Foi desenvolvido pela Diretoria Executiva de Informática - DIRTEC um QrCode que permitirá acesso à Pauta das Sessões de Julgamento. Cabe esclarecer que o QR Coce ainda não está integrado com o eproc e que isso não faz parte do escopo da entrega. Essa funcionalidade demanda aprovação do Conselho do eproc para ser incorporado. Há expectativa para a divulgação das transmissões no decorrer do ano de 2026.</t>
+          <t>Verifica-se que, até dezembro de 2025, foram concluídas 26 entregas das 31 prevista para o Programa, sendo 6 em 2023, 13 em 2024 e 7 em 2025, obtendo um resultado apurado de 87,39%. As entregas concluídas em 2025, são: Implantação dos equipamentos Audiovisuais e TIC no Auditório do Juizado Especial Cível Implantação dos equipamentos Audiovisuais e TIC no Auditório do Pleno (ed. Sede). Implantação de VideoWall – Auditório do Pleno. Implantação do Projeto Piloto para transmissão ao vivo (streaming) das Sessões de Julgamento do Órgão Especial, utilizando a Plataforma Youtube. Implantação e gerenciamento de Equipe Técnica para operacionalização dos novos equipamentos de áudio e TIC. Implantação do Software de Videoconferência. Implantação do Sistema de Emenda Regimental. Além dessas, 1 entrega foi cancelada, 1 não iniciada e 3 estão em andamento, com perspectiva de conclusão em 2026. A entrega Fluxos de trabalho decorrentes das novas tecnologias do Programa foi cancelada porque não será mais realizada nos termos em que foi planejada. Inicialmente, foi previsto que o CEPROC (Centro de Gestão de Processos de Trabalho, Padronização e Qualidade) redesenharia todos os processos de trabalho que, eventualmente, sofressem alteração em decorrência das melhorias tecnológicas implementadas para modernização dos plenários. No entanto, na prática, o que se verifica é uma atuação mais direcionada para áreas que demandam o serviço. Cabe ressaltar que a entrega, quando cancelada, não impacta o cumprimento da meta em questão. O projeto piloto para a transmissão ao vivo (Streaming) das Sessões de Julgamento no TJMG, foi considerado concluído em 13/08, com a primeira gravação da sessão do Órgão especial. As sessões do Órgão Especial passaram a ser integralmente transmitidas pelo canal oficial do TJMG no YouTube a partir de 10 de setembro de 2025, sendo vedada a transmissão de pautas submetidas a segredo de justiça. Com isso, o TJMG passa a cumprir os itens 12 e 13 constantes no Anexo da Portaria nº 406 do Conselho Nacional de justiça (CNJ) de 29 de novembro de 2024, que estabelece o regulamento do Ranking da Transparência do Poder Judiciário – 2025. A entrega Implantação da Plataforma Youtube para transmissão ao vivo (Streaming) das Sessões de julgamento, que prevê a expansão da transmissão ao vivo para as sessões dos plenários, foi impactada pelo atraso do piloto, ficando suspensa ao longo de 2025. Além disso, para expansão, aguarda-se a definição da Alta Administração quanto a estratégia para a expansão (data, ordem dos Plenários, etc.), razão pela qual a entrega apresenta perspectiva de conclusão em 2026. No que tange às entregas em andamento: Em 2023, o processo licitatório para a aquisição do sistema para votação administrativa foi deserto. Diante disso, deliberou-se por promover melhorias no módulo SEI Julgar para viabilizar a sua utilização pelo TJMG. Embora algumas customizações já tenham sido realizadas ao longo de 2024 e 2025, ainda restam funcionalidades a serem desenvolvidas, sem as quais não é possível realizar o projeto piloto.  A entrega ficou suspensa ao longo de 2025, tendo em vista que a equipe técnica responsável pelo desenvolvimento estava alocada em outras frentes de trabalho igualmente relevantes para instituição. Estima-se a retomada da customização do sistema para votação administrativa para 2026. Por meio de Acordo de Cooperação (AC) com o TRF-4, houve a cessão do software Tela para Gravação e Indexação das sessões do TJMG. Ele foi implantado inicialmente nos plenários 4 e 10. Atualmente, o projeto encontra-se em fase de adaptações e aprimoramento entre o Sistema TELA e o Eproc, com previsão de início da expansão para os demais plenários entre fevereiro e março de 2026. Em relação à transcrição, o projeto-piloto da implantação da 'Solução de Transposição' da empresa Xértica nos plenários 4 e 10, em setembro de 2025, foi bem-sucedido. Assim sendo, o início da expansão para as demais unidades está previsto para fevereiro de 2026. O início da expansão para o Auditório está condicionado à implementação prévia de melhorias e adaptações estruturais de longo prazo no sistema TELA, conforme demanda da área de negócio. Em razão da necessidade desses ajustes técnicos, ainda não há data definida para a conclusão desta etapa, a qual será estabelecida após a entrega das adequações mencionadas. Ainda sobre a entrega software Tela para Gravação, Indexação e Transcrição das sessões, cabe ressaltar que o módulo de Gestão de Pedidos vai permitir a gestão dos pedidos de acesso à informação de gravação e transcrição das sessões de julgamento feitos pelo Desembargador demandante. Esclarece-se que essa sistemática já existe dentro do Themis, mas, tendo em vista que esse sistema será descontinuado, foi deliberada a utilização do E-proc para o mesmo fim.  Para tanto, serão necessários ajustes no E-proc, visando tanto a integração com o Tela quanto o desenvolvimento/adequações de funcionalidades atinentes ao módulo de gestão de pedidos, que começarão a ser realizados após a conclusão da homologação do sistema Tela. Foi desenvolvido, pela Diretoria Executiva de Informática – DIRTEC, um QrCode e uma página na internet que permitirão o acompanhamento da lista de processos em julgamento, em tempo real. O QRCode ficará disponível próximo aos plenários, permitindo que usuários externos, via dispositivo móvel, acessem a página Sessão de Julgamento ( https://sessao-themis.tjmg.jus.br/sessao-themis/ ) e realizem consultas por data e órgão julgador (exemplo: Câmara, Núcleo de Justiça 4.0, Tribunal Pleno, etc.). Esclarece-se que a página ainda não conterá informações advindas do eproc. No entanto, isso não inviabiliza a divulgação, pois há quantidade expressiva de sessões disponíveis para divulgação nos sistemas Themis. Em relação a disponibilização do referido QR code nos Plenários, há expectativa para a divulgação no decorrer do ano de 2026.</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3199,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
